--- a/artfynd/A 62566-2025 artfynd.xlsx
+++ b/artfynd/A 62566-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130327570</v>
       </c>
       <c r="B2" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>130327820</v>
       </c>
       <c r="B3" t="n">
-        <v>97797</v>
+        <v>97800</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>130339563</v>
       </c>
       <c r="B4" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>130339606</v>
       </c>
       <c r="B5" t="n">
-        <v>79204</v>
+        <v>79207</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>130339548</v>
       </c>
       <c r="B7" t="n">
-        <v>91749</v>
+        <v>91752</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 62566-2025 artfynd.xlsx
+++ b/artfynd/A 62566-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130327570</v>
       </c>
       <c r="B2" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>130327820</v>
       </c>
       <c r="B3" t="n">
-        <v>97800</v>
+        <v>97826</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>130339563</v>
       </c>
       <c r="B4" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>130339606</v>
       </c>
       <c r="B5" t="n">
-        <v>79207</v>
+        <v>79233</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>130339580</v>
       </c>
       <c r="B6" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>130339548</v>
       </c>
       <c r="B7" t="n">
-        <v>91752</v>
+        <v>91778</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 62566-2025 artfynd.xlsx
+++ b/artfynd/A 62566-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130327570</v>
       </c>
       <c r="B2" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>130327820</v>
       </c>
       <c r="B3" t="n">
-        <v>97826</v>
+        <v>97827</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>130339563</v>
       </c>
       <c r="B4" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>130339548</v>
       </c>
       <c r="B7" t="n">
-        <v>91778</v>
+        <v>91779</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 62566-2025 artfynd.xlsx
+++ b/artfynd/A 62566-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130327570</v>
       </c>
       <c r="B2" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>130327820</v>
       </c>
       <c r="B3" t="n">
-        <v>97827</v>
+        <v>97828</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>130339563</v>
       </c>
       <c r="B4" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>130339548</v>
       </c>
       <c r="B7" t="n">
-        <v>91779</v>
+        <v>91780</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 62566-2025 artfynd.xlsx
+++ b/artfynd/A 62566-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130327570</v>
       </c>
       <c r="B2" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>130327820</v>
       </c>
       <c r="B3" t="n">
-        <v>97828</v>
+        <v>97830</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>130339563</v>
       </c>
       <c r="B4" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>130339606</v>
       </c>
       <c r="B5" t="n">
-        <v>79233</v>
+        <v>79235</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>130339580</v>
       </c>
       <c r="B6" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>130339548</v>
       </c>
       <c r="B7" t="n">
-        <v>91780</v>
+        <v>91782</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 62566-2025 artfynd.xlsx
+++ b/artfynd/A 62566-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130327570</v>
       </c>
       <c r="B2" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>130327820</v>
       </c>
       <c r="B3" t="n">
-        <v>97830</v>
+        <v>97834</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>130339563</v>
       </c>
       <c r="B4" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 62566-2025 artfynd.xlsx
+++ b/artfynd/A 62566-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130327570</v>
       </c>
       <c r="B2" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>130327820</v>
       </c>
       <c r="B3" t="n">
-        <v>97834</v>
+        <v>97847</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>130339563</v>
       </c>
       <c r="B4" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>130339606</v>
       </c>
       <c r="B5" t="n">
-        <v>79235</v>
+        <v>79243</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>130339580</v>
       </c>
       <c r="B6" t="n">
-        <v>57044</v>
+        <v>57052</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>130339548</v>
       </c>
       <c r="B7" t="n">
-        <v>91782</v>
+        <v>91795</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 62566-2025 artfynd.xlsx
+++ b/artfynd/A 62566-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130327570</v>
       </c>
       <c r="B2" t="n">
-        <v>98970</v>
+        <v>98971</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>130327820</v>
       </c>
       <c r="B3" t="n">
-        <v>97847</v>
+        <v>97848</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>130339563</v>
       </c>
       <c r="B4" t="n">
-        <v>98970</v>
+        <v>98971</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>130339606</v>
       </c>
       <c r="B5" t="n">
-        <v>79243</v>
+        <v>79244</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>130339580</v>
       </c>
       <c r="B6" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>130339548</v>
       </c>
       <c r="B7" t="n">
-        <v>91795</v>
+        <v>91796</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 62566-2025 artfynd.xlsx
+++ b/artfynd/A 62566-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130327570</v>
       </c>
       <c r="B2" t="n">
-        <v>98971</v>
+        <v>98974</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>130327820</v>
       </c>
       <c r="B3" t="n">
-        <v>97848</v>
+        <v>97851</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>130339563</v>
       </c>
       <c r="B4" t="n">
-        <v>98971</v>
+        <v>98974</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>130339606</v>
       </c>
       <c r="B5" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>130339548</v>
       </c>
       <c r="B7" t="n">
-        <v>91796</v>
+        <v>91797</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 62566-2025 artfynd.xlsx
+++ b/artfynd/A 62566-2025 artfynd.xlsx
@@ -675,50 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130327570</v>
+        <v>130339548</v>
       </c>
       <c r="B2" t="n">
-        <v>98974</v>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -726,13 +713,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552983</v>
+        <v>552886</v>
       </c>
       <c r="R2" t="n">
-        <v>6841526</v>
+        <v>6841455</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,6 +749,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>död fruktkropp på död tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,22 +769,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Jenss Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130327820</v>
+        <v>130339606</v>
       </c>
       <c r="B3" t="n">
-        <v>97851</v>
+        <v>79351</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -800,35 +792,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>6434</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -836,13 +819,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552947</v>
+        <v>552839</v>
       </c>
       <c r="R3" t="n">
-        <v>6841522</v>
+        <v>6841416</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -887,58 +870,54 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130339563</v>
+        <v>130339580</v>
       </c>
       <c r="B4" t="n">
-        <v>98974</v>
+        <v>57141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -946,10 +925,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552886</v>
+        <v>552849</v>
       </c>
       <c r="R4" t="n">
-        <v>6841455</v>
+        <v>6841410</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -990,7 +969,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1009,37 +987,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130339606</v>
+        <v>130327570</v>
       </c>
       <c r="B5" t="n">
-        <v>79245</v>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6434</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1047,13 +1038,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552839</v>
+        <v>552983</v>
       </c>
       <c r="R5" t="n">
-        <v>6841416</v>
+        <v>6841526</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1098,54 +1089,58 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jenss Hansen</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jenss Hansen</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130339580</v>
+        <v>130339563</v>
       </c>
       <c r="B6" t="n">
-        <v>57053</v>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1153,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552849</v>
+        <v>552886</v>
       </c>
       <c r="R6" t="n">
-        <v>6841410</v>
+        <v>6841455</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1197,6 +1192,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1215,37 +1211,46 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130339548</v>
+        <v>130327820</v>
       </c>
       <c r="B7" t="n">
-        <v>91797</v>
+        <v>97989</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>221941</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1253,13 +1258,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552886</v>
+        <v>552947</v>
       </c>
       <c r="R7" t="n">
-        <v>6841455</v>
+        <v>6841522</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1289,11 +1294,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-12-28</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>död fruktkropp på död tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1309,12 +1309,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jenss Hansen</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jenss Hansen, Carina Frost</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 62566-2025 artfynd.xlsx
+++ b/artfynd/A 62566-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130339548</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130339606</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -984,6 +999,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130339580</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1098,6 +1118,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130327570</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1208,6 +1233,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130339563</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1318,8 +1348,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130327820</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>